--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B15F4F-040C-4426-B25E-6E7332404071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E464FD3-D6AA-4ECC-9F76-FE58570E3830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="2250" yWindow="2040" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,9 +99,6 @@
     <t>Al QUDDUS A5 HVS,CUSTOM COVER + 1 HALAMAN</t>
   </si>
   <si>
-    <t>AL QUR'AN EDISI TAHLILAN 30 Juz + Doa Tahlil | Pengganti Buku Yasin | Al Aqeel A6 Pastel HVS Edisi Tahlilan</t>
-  </si>
-  <si>
     <t>Custom sisipan 1 hal</t>
   </si>
   <si>
@@ -115,6 +112,9 @@
   </si>
   <si>
     <t>Sisipan 1hal+jaket</t>
+  </si>
+  <si>
+    <t>AL QUR'AN EDISI TAHLILAN 30 Juz + Doa Tahlil | Pengganti Buku Yasin | Al Aqeel A6 Pastel HVS Edisi Tahlilan | Jakarta</t>
   </si>
 </sst>
 </file>
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -210,7 +210,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,10 +774,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="C22">
         <v>1250</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C23">
         <v>2500</v>
@@ -797,10 +796,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C24">
         <v>1000</v>
@@ -808,10 +807,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>7300</v>
@@ -819,10 +818,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2250</v>

--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E464FD3-D6AA-4ECC-9F76-FE58570E3830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77500106-31AF-4C1A-9FC1-79F473E766EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2040" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="2940" yWindow="2730" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -115,6 +115,54 @@
   </si>
   <si>
     <t>AL QUR'AN EDISI TAHLILAN 30 Juz + Doa Tahlil | Pengganti Buku Yasin | Al Aqeel A6 Pastel HVS Edisi Tahlilan | Jakarta</t>
+  </si>
+  <si>
+    <t>Al-Qur'an Edisi Tahlilan Al Aqeel A6 Kertas HVS 18 Baris | GARUT | Alquran Untuk Wakaf Hadiah Souvenir Hampers</t>
+  </si>
+  <si>
+    <t>standar/tanpa custom</t>
+  </si>
+  <si>
+    <t>sisipan 1 halaman</t>
+  </si>
+  <si>
+    <t>sisipan 2 halaman</t>
+  </si>
+  <si>
+    <t>Al-Qur'an Custom Foto Nama | GARUT | Alquran Untuk Wakaf Tasyakuran Tahlilan A5 &amp; A6 Tebal dan Jelas</t>
+  </si>
+  <si>
+    <t>Al Aqeel A5 Koran,Sisipan 1 halaman</t>
+  </si>
+  <si>
+    <t>Al Aqeel A5 Koran,Sisipan 2 halaman</t>
+  </si>
+  <si>
+    <t>Al Aqeel A6 Hvs,Sisipan 1 halaman</t>
+  </si>
+  <si>
+    <t>Al Aqeel A6 Hvs,Sisipan 2 halaman</t>
+  </si>
+  <si>
+    <t>Al-Qur'an Edisi Tahlilan A6 | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemah | Semarang</t>
+  </si>
+  <si>
+    <t>Tidak Custom/Biasa</t>
+  </si>
+  <si>
+    <t>A5 Koran,Sisipan 1 Hal</t>
+  </si>
+  <si>
+    <t>A5 Koran,Sisipan 2 Hal</t>
+  </si>
+  <si>
+    <t>A6 Pastel,Sisipan 1 Hal</t>
+  </si>
+  <si>
+    <t>A6 Pastel,Sisipan 2 Hal</t>
+  </si>
+  <si>
+    <t>Custom Al-Qur'an Mengenang Wafat Ukuran A5 A6 | Semarang</t>
   </si>
 </sst>
 </file>
@@ -197,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -210,6 +258,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3868EE60-3048-4482-B09F-8FE75025847A}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -827,6 +876,165 @@
         <v>2250</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="3">
+        <f>2500*2</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="3">
+        <f>1250*2</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="3">
+        <f>1250*2</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="3">
+        <f>2500*2</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="3">
+        <f>1250*2</f>
+        <v>2500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77500106-31AF-4C1A-9FC1-79F473E766EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF2E7C-F06E-4971-B230-C50216BDE9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="2730" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
@@ -245,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -258,7 +258,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,7 +872,7 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>2250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -895,7 +894,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>1250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -906,7 +905,7 @@
         <v>33</v>
       </c>
       <c r="C29">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,8 +915,8 @@
       <c r="B30" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="3">
-        <v>2500</v>
+      <c r="C30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -927,9 +926,8 @@
       <c r="B31" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+      <c r="C31">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -939,8 +937,8 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="3">
-        <v>1250</v>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -950,9 +948,8 @@
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="3">
-        <f>1250*2</f>
-        <v>2500</v>
+      <c r="C33">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,7 +959,7 @@
       <c r="B34" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34">
         <v>0</v>
       </c>
     </row>
@@ -973,8 +970,8 @@
       <c r="B35" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="3">
-        <v>1250</v>
+      <c r="C35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,9 +981,8 @@
       <c r="B36" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="3">
-        <f>1250*2</f>
-        <v>2500</v>
+      <c r="C36">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,8 +992,8 @@
       <c r="B37" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="3">
-        <v>2500</v>
+      <c r="C37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,9 +1003,8 @@
       <c r="B38" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+      <c r="C38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1019,8 +1014,8 @@
       <c r="B39" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="3">
-        <v>1250</v>
+      <c r="C39">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1030,9 +1025,8 @@
       <c r="B40" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="3">
-        <f>1250*2</f>
-        <v>2500</v>
+      <c r="C40">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF2E7C-F06E-4971-B230-C50216BDE9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF25F760-E94C-4530-9F70-2667041B0571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2730" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Variasi</t>
   </si>
   <si>
-    <t>CUSTOM AL QURAN MENGENANG/WAFAT 40/100/1000 HARI</t>
-  </si>
-  <si>
     <t>AL AQEEL A6 HVS,1 HALAMAN + AL QURAN</t>
   </si>
   <si>
@@ -163,6 +160,84 @@
   </si>
   <si>
     <t>Custom Al-Qur'an Mengenang Wafat Ukuran A5 A6 | Semarang</t>
+  </si>
+  <si>
+    <t>AL QURAN CUSTOM NAMA FOTO SISIPAN COVER ACARA TASYAKUR TAHLIL YASIN (BANDUNG)</t>
+  </si>
+  <si>
+    <t>A5 KORAN FAHEEM,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 KORAN FAHEEM,Custom cover</t>
+  </si>
+  <si>
+    <t>A5 KORAN FAHEEM,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A5 KORAN FAHEEM,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL FIKRAH,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL FIKRAH,Custom cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL FIKRAH,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL FIKRAH,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL QUDDUS,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL QUDDUS,Custom cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL QUDDUS,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL QUDDUS,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL AQEEL,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 HVS AL AQEEL,Custom cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL AQEEL,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A5 HVS AL AQEEL,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>A5 KORAN AL AQEEL,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A5 KORAN AL AQEEL,Custom cover</t>
+  </si>
+  <si>
+    <t>A5 KORAN AL AQEEL,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A5 KORAN AL AQEEL,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>A6 HVS AL AQEEL,Custom sisipan 1Lbr</t>
+  </si>
+  <si>
+    <t>A6 HVS AL AQEEL,Custom cover</t>
+  </si>
+  <si>
+    <t>A6 HVS AL AQEEL,Custom sisipan+cover</t>
+  </si>
+  <si>
+    <t>A6 HVS AL AQEEL,Custom sisipan 2Lbr</t>
+  </si>
+  <si>
+    <t>CUSTOM AL QURAN MENGENANG/WAFAT 40/100/1000 HARI | Jakarta</t>
   </si>
 </sst>
 </file>
@@ -245,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -258,6 +333,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3868EE60-3048-4482-B09F-8FE75025847A}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -587,267 +665,266 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="C2" s="3">
-        <v>1250</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3">
-        <f>1250*2</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
-        <f>7300+1250</f>
-        <v>8550</v>
+        <f>7500+1000</f>
+        <v>8500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+        <f>1500*2</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
         <f>C8+C6</f>
-        <v>9800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+        <f>1500*2</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <f>C10+C12</f>
-        <v>9800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+        <f>1500*2</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3">
         <f>C14+C16</f>
-        <v>9800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3">
-        <f>2500*2</f>
-        <v>5000</v>
+        <f>1500*2</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3">
         <f>C18+C20</f>
-        <v>9800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>1250</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>1000</v>
@@ -855,32 +932,32 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>7300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
         <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -888,76 +965,76 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
         <v>34</v>
       </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
       <c r="C30">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
         <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -965,68 +1042,332 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF25F760-E94C-4530-9F70-2667041B0571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38560CCF-C908-4213-8CFF-D79C47BC081A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="78">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -238,6 +238,27 @@
   </si>
   <si>
     <t>CUSTOM AL QURAN MENGENANG/WAFAT 40/100/1000 HARI | Jakarta</t>
+  </si>
+  <si>
+    <t>Alquran Edisi Tahlilan A6 Pengganti Buku Yasin Terjemah | MEDAN</t>
+  </si>
+  <si>
+    <t>Tidak custom</t>
+  </si>
+  <si>
+    <t>Sisipan 1 hal</t>
+  </si>
+  <si>
+    <t>Sisipan 2 hal</t>
+  </si>
+  <si>
+    <t>Jacket</t>
+  </si>
+  <si>
+    <t>Tanpa Custom/Biasa</t>
+  </si>
+  <si>
+    <t>Alquran Al Aqeel Edisi Tahlilan A6 HVS | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemahan | Yogyakarta</t>
   </si>
 </sst>
 </file>
@@ -650,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3868EE60-3048-4482-B09F-8FE75025847A}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1370,7 +1391,85 @@
         <v>2000</v>
       </c>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71">
+        <v>2000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38560CCF-C908-4213-8CFF-D79C47BC081A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD3255A-4AE2-4856-917C-46C08ED3BDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="15375" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="87">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -259,6 +259,33 @@
   </si>
   <si>
     <t>Alquran Al Aqeel Edisi Tahlilan A6 HVS | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemahan | Yogyakarta</t>
+  </si>
+  <si>
+    <t>AL QUR'AN EDISI TAHLILAN 30 Juz + Doa Tahlil | Pengganti Buku Yasin | Al Aqeel A6 Pastel HVS Edisi Tahlilan | BANDUNG</t>
+  </si>
+  <si>
+    <t>Alquran Custom Nama Foto | SURABAYA | Al-Quran untuk Wakaf Tasyakuran Tahlil Yasin Hadiah Hampers Islami</t>
+  </si>
+  <si>
+    <t>AL AQEEL A5 KORAN,SISIPAN 1 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>AL AQEEL A5 KORAN,SISIPAN 2 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>AL AQEEL A6 HVS,SISIPAN 1 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>AL AQEEL A6 HVS,SISIPAN 2 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>AL AQEEL GOLD A5 HVS,SISIPAN 1 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>AL AQEEL GOLD A5 HVS,SISIPAN 2 HAL+QURAN</t>
+  </si>
+  <si>
+    <t>Alquran Edisi Tahlilan Lebih Mulia Daripada Buku Yasin Biasa | Al Aqeel A6 Kertas HVS | SURABAYA |</t>
   </si>
 </sst>
 </file>
@@ -671,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3868EE60-3048-4482-B09F-8FE75025847A}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1380,45 +1407,45 @@
         <v>8500</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="C64">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" t="s">
-        <v>72</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>71</v>
-      </c>
-      <c r="B66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" t="s">
-        <v>74</v>
       </c>
       <c r="C67">
         <v>2000</v>
@@ -1429,42 +1456,174 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C68">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="C70">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>77</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" t="s">
         <v>24</v>
       </c>
-      <c r="C71">
+      <c r="C74">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83">
         <v>2000</v>
       </c>
     </row>
